--- a/artfynd/A 21405-2026 artfynd.xlsx
+++ b/artfynd/A 21405-2026 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>363077</v>
       </c>
       <c r="B2" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>601571.9428745755</v>
+        <v>601572</v>
       </c>
       <c r="R2" t="n">
-        <v>7160664.005856365</v>
+        <v>7160664</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2012-09-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-09-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,12 +780,7 @@
         <v>441461</v>
       </c>
       <c r="B3" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>601468.9494763557</v>
+        <v>601469</v>
       </c>
       <c r="R3" t="n">
-        <v>7160870.590992002</v>
+        <v>7160871</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,19 +845,9 @@
           <t>2012-09-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2012-09-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
